--- a/stories/arbres/TREE-SOC-004.xlsx
+++ b/stories/arbres/TREE-SOC-004.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sami est dans le jardin, avec papa. Papa dit : maman travaille. Moi aussi, je travaille. Le travail donne de l'argent. L'argent sert à acheter pain, légumes, chaussures. Sami touche une feuille. Papa montre le pain de la collation. Acheter. Pain. Légumes. Chaussures. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
+          <t>Sami est dans le jardin, avec papa. Maman travaille. Moi aussi, je travaille. Le travail donne de l'argent. L'argent sert à acheter pain, légumes, chaussures. Sami touche une feuille. Papa montre le pain de la collation. Acheter. Pain. Légumes. Chaussures. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Sami est dans le jardin, avec papa.
+papa|Maman travaille. Moi aussi, je travaille.
+narrateur|Le travail donne de l'argent. L'argent sert à acheter pain, légumes, chaussures. Sami touche une feuille. Papa montre le pain de la collation. Acheter. Pain. Légumes. Chaussures. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1511,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1540,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sami prend les cubes. Papa dit : avec le travail, on peut acheter du pain, des légumes, des chaussures. Sami empile. Travail. Acheter. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
+          <t>Sami prend les cubes. Avec le travail, on peut acheter du pain, des légumes, des chaussures. Sami empile. Travail. Acheter. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1678,13 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Sami prend les cubes.
+papa|Avec le travail, on peut acheter du pain, des légumes, des chaussures.
+narrateur|Sami empile. Travail. Acheter. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1861,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Papa ou maman fait un quoi ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2034,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Sami a dit travail. On peut acheter pain, légumes, chaussures. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2225,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2392,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Sami prend une pomme. Un ballon frotte le sol. Sami pose une pomme. On peut acheter des fruits aussi. Pain, légumes, chaussures. Travail. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2527,6 +2583,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2689,6 +2750,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'approche de le chat. La lumière est claire. On met le doudou près. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Le pain est là. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2851,6 +2917,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3013,6 +3084,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'approche de le chien. Des miettes dorment sur la table. On lace les chaussures. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Les chaussures attendent près de la porte. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Papa serre Sami tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3175,6 +3251,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3337,6 +3418,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'approche de la poule. Un chat miaule une fois. On met le manteau. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Les légumes sont dans le panier. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3499,6 +3585,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3523,7 +3614,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Sami prend un yaourt. Une goutte tombe, ploc. Un yaourt. Papa dit : acheter. Grâce au travail. Pain, légumes, chaussures. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
+          <t>Sami prend un yaourt. Une goutte tombe, ploc. Un yaourt. Acheter. Grâce au travail. Pain, légumes, chaussures. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3661,6 +3752,12 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Sami prend un yaourt. Une goutte tombe, ploc. Un yaourt.
+papa|Acheter. Grâce au travail. Pain, légumes, chaussures. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3847,6 +3944,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3871,7 +3973,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Sami s'approche de le chat. Les chaussures font toc toc. On boit une gorgée. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Le travail de l'adulte aide. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Sami range. Papa dit : c'est bien.</t>
+          <t>Sami s'approche de le chat. Les chaussures font toc toc. On boit une gorgée. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Le travail de l'adulte aide. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Sami range. C'est bien.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4009,6 +4111,12 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'approche de le chat. Les chaussures font toc toc. On boit une gorgée. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Le travail de l'adulte aide. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Sami range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4171,6 +4279,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4333,6 +4446,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'approche de le chien. La couverture est douce. On feuillette le livre. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Le pain est là. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. On souffle. Sami sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4495,6 +4613,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4657,6 +4780,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'approche de la poule. Une cloche tinte au loin. On referme le livre. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Les chaussures attendent près de la porte. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Sami prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4819,6 +4947,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4981,6 +5114,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Sami prend un morceau de pain. Le savon sent la fleur. Un morceau de pain. Voilà le pain. Acheter. Travail. Légumes, chaussures. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5167,6 +5305,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5329,6 +5472,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'approche de le chat. Le bois sent le chaud. On pose le ballon. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Les légumes sont dans le panier. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5491,6 +5639,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5653,6 +5806,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'approche de le chien. Une goutte tombe, ploc. On secoue le sable. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Le travail de l'adulte aide. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Papa serre Sami tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5815,6 +5973,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5977,6 +6140,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'approche de la poule. Le savon sent la fleur. On caresse le tissu. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Le pain est là. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6139,6 +6307,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6301,6 +6474,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Sami ouvre le livre. Une image de marché. On va acheter pain, légumes, chaussures. Grâce au travail. Sami pointe le pain. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6477,6 +6655,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|L'argent sert à faire quoi ?</t>
         </is>
       </c>
     </row>
@@ -6645,6 +6828,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Acheter. Pain. Légumes. Chaussures. Papa travaille. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6831,6 +7019,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6993,6 +7186,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Sami prend une pomme. Un nuage passe lentement. La pomme est rouge. Sami dit acheter. Travail. Pain, légumes, chaussures. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7179,6 +7377,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7203,7 +7406,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Sami s'approche de le chat. Le tissu est tout doux. On tend la main. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Les chaussures attendent près de la porte. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Sami range. Papa dit : c'est bien.</t>
+          <t>Sami s'approche de le chat. Le tissu est tout doux. On tend la main. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Les chaussures attendent près de la porte. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Sami range. C'est bien.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7341,6 +7544,12 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'approche de le chat. Le tissu est tout doux. On tend la main. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Les chaussures attendent près de la porte. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Sami range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7503,6 +7712,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7665,6 +7879,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'approche de le chien. Une cuillère tinte. On chante un petit air. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Les légumes sont dans le panier. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. On souffle. Sami sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7827,6 +8046,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7989,6 +8213,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'approche de la poule. Le sable est tiède. On compte jusqu'à trois. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Le travail de l'adulte aide. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Sami prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8151,6 +8380,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8313,6 +8547,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Sami prend un yaourt. Une cloche tinte au loin. Le yaourt est froid. Papa rappelle le travail. Acheter pain, légumes, chaussures. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8499,6 +8738,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8661,6 +8905,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'approche de le chat. Un rire court, tout petit. On montre du doigt. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Le pain est là. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8823,6 +9072,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8985,6 +9239,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'approche de le chien. Le papier froisse, chut. On range la chaise. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Les chaussures attendent près de la porte. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Papa serre Sami tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9147,6 +9406,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9309,6 +9573,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'approche de la poule. L'herbe chatouille le mollet. On range un objet. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Les légumes sont dans le panier. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9471,6 +9740,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9633,6 +9907,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Sami prend un morceau de pain. Un oiseau chante tout près. Le pain croustille. Acheter. Travail. Légumes. Chaussures. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9819,6 +10098,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9843,7 +10127,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Sami s'approche de le chat. Un pigeon roucoule. On se tient la main. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Le travail de l'adulte aide. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Sami range. Papa dit : c'est bien.</t>
+          <t>Sami s'approche de le chat. Un pigeon roucoule. On se tient la main. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Le travail de l'adulte aide. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Sami range. C'est bien.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -9981,6 +10265,12 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'approche de le chat. Un pigeon roucoule. On se tient la main. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Le travail de l'adulte aide. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Sami range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10143,6 +10433,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10305,6 +10600,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'approche de le chien. La fenêtre vibre un peu. On dit merci. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Le pain est là. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. On souffle. Sami sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10467,6 +10767,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10629,6 +10934,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'approche de la poule. Le lait est froid dans le verre. On souffle doucement. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Les chaussures attendent près de la porte. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Sami prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10791,6 +11101,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10815,7 +11130,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Sami pose la dînette. Une carotte en bois. Un légume. Papa dit : on achète les légumes. Le pain. Les chaussures. Le travail aide. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
+          <t>Sami pose la dînette. Une carotte en bois. Un légume. On achète les légumes. Le pain. Les chaussures. Le travail aide. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10953,6 +11268,13 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Sami pose la dînette. Une carotte en bois. Un légume.
+papa|On achète les légumes.
+narrateur|Le pain. Les chaussures. Le travail aide. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11129,6 +11451,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|On achète le pain, et aussi quoi ?</t>
         </is>
       </c>
     </row>
@@ -11297,6 +11624,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Sami retient. Travail. Acheter pain, légumes, chaussures. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11483,6 +11815,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11645,6 +11982,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Sami prend une pomme. Le savon glisse. Sami sent la pomme. Travail. Acheter pain, légumes, chaussures. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11831,6 +12173,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11993,6 +12340,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'approche de le chat. La corde du sac est rêche. On écoute jusqu'au bout. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Les légumes sont dans le panier. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12155,6 +12507,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12317,6 +12674,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'approche de le chien. Le savon mousse entre les doigts. On attend son tour. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Le travail de l'adulte aide. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Papa serre Sami tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12479,6 +12841,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12641,6 +13008,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'approche de la poule. Un ruisseau chante. On sourit ensemble. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Le pain est là. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12803,6 +13175,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12965,6 +13342,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Sami prend un yaourt. Un ruisseau chante. Sami pose le yaourt. Papa dit encore : acheter. Pain. Légumes. Chaussures. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13151,6 +13533,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13175,7 +13562,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Sami s'approche de le chat. La laine gratte un peu. On pose les pieds par terre. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Les chaussures attendent près de la porte. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Sami range. Papa dit : c'est bien.</t>
+          <t>Sami s'approche de le chat. La laine gratte un peu. On pose les pieds par terre. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Les chaussures attendent près de la porte. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Sami range. C'est bien.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13313,6 +13700,12 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'approche de le chat. La laine gratte un peu. On pose les pieds par terre. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Les chaussures attendent près de la porte. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Sami range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13475,6 +13868,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13637,6 +14035,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'approche de le chien. Un pain croustille. On parle tout bas. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Les légumes sont dans le panier. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. On souffle. Sami sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13799,6 +14202,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13961,6 +14369,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'approche de la poule. Le savon glisse. On range les jouets. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Le travail de l'adulte aide. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Sami prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14123,6 +14536,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14285,6 +14703,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Sami prend un morceau de pain. Un ballon frotte le sol. Le pain est sur la table. Travail. Acheter pain, légumes, chaussures. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14471,6 +14894,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14633,6 +15061,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'approche de le chat. Une plume vole. On s'assoit un moment. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Le pain est là. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Sami dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14795,6 +15228,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14957,6 +15395,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'approche de le chien. Le banc est lisse. On respire, un, deux. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Les chaussures attendent près de la porte. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Papa serre Sami tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15119,6 +15562,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15281,6 +15729,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Sami s'approche de la poule. Un grelot sonne. On referme le sac. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Les légumes sont dans le panier. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15443,6 +15896,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15461,7 +15919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15478,6 +15936,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SOC-004.xlsx
+++ b/stories/arbres/TREE-SOC-004.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Le travail donne de l'argent. L'argent sert à acheter pain, légumes, chaussures. Sami touche une feuille. Papa montre le pain de la collation. Acheter. Pain. Légumes. Chaussures. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1516,6 +1522,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1685,6 +1692,7 @@
 narrateur|Sami empile. Travail. Acheter. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1868,6 +1876,7 @@
           <t>narrateur|Papa ou maman fait un quoi ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2039,6 +2048,7 @@
           <t>narrateur|Sami a dit travail. On peut acheter pain, légumes, chaussures. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2230,6 +2240,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2397,6 +2408,7 @@
           <t>narrateur|Sami prend une pomme. Un ballon frotte le sol. Sami pose une pomme. On peut acheter des fruits aussi. Pain, légumes, chaussures. Travail. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2586,6 +2598,11 @@
       <c r="AW9" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -2755,6 +2772,7 @@
           <t>narrateur|Sami s'approche de le chat. La lumière est claire. On met le doudou près. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Le pain est là. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2922,6 +2940,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3089,6 +3108,11 @@
           <t>narrateur|Sami s'approche de le chien. Des miettes dorment sur la table. On lace les chaussures. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Les chaussures attendent près de la porte. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Papa serre Sami tout doux.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3256,6 +3280,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3423,6 +3448,7 @@
           <t>narrateur|Sami s'approche de la poule. Un chat miaule une fois. On met le manteau. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Les légumes sont dans le panier. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3590,6 +3616,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3758,6 +3785,7 @@
 papa|Acheter. Grâce au travail. Pain, légumes, chaussures. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3947,6 +3975,11 @@
       <c r="AW17" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -4117,6 +4150,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4284,6 +4318,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4451,6 +4486,11 @@
           <t>narrateur|Sami s'approche de le chien. La couverture est douce. On feuillette le livre. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Le pain est là. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. On souffle. Sami sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4618,6 +4658,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4785,6 +4826,7 @@
           <t>narrateur|Sami s'approche de la poule. Une cloche tinte au loin. On referme le livre. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Les chaussures attendent près de la porte. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Sami prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4952,6 +4994,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5119,6 +5162,7 @@
           <t>narrateur|Sami prend un morceau de pain. Le savon sent la fleur. Un morceau de pain. Voilà le pain. Acheter. Travail. Légumes, chaussures. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5308,6 +5352,11 @@
       <c r="AW25" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -5477,6 +5526,7 @@
           <t>narrateur|Sami s'approche de le chat. Le bois sent le chaud. On pose le ballon. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Les légumes sont dans le panier. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5644,6 +5694,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5811,6 +5862,11 @@
           <t>narrateur|Sami s'approche de le chien. Une goutte tombe, ploc. On secoue le sable. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Le travail de l'adulte aide. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Papa serre Sami tout doux.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5978,6 +6034,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6145,6 +6202,7 @@
           <t>narrateur|Sami s'approche de la poule. Le savon sent la fleur. On caresse le tissu. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Le pain est là. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6312,6 +6370,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6479,6 +6538,7 @@
           <t>narrateur|Sami ouvre le livre. Une image de marché. On va acheter pain, légumes, chaussures. Grâce au travail. Sami pointe le pain. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6662,6 +6722,7 @@
           <t>narrateur|L'argent sert à faire quoi ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6833,6 +6894,7 @@
           <t>narrateur|Acheter. Pain. Légumes. Chaussures. Papa travaille. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7024,6 +7086,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7191,6 +7254,7 @@
           <t>narrateur|Sami prend une pomme. Un nuage passe lentement. La pomme est rouge. Sami dit acheter. Travail. Pain, légumes, chaussures. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7380,6 +7444,11 @@
       <c r="AW37" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -7550,6 +7619,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7717,6 +7787,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7884,6 +7955,11 @@
           <t>narrateur|Sami s'approche de le chien. Une cuillère tinte. On chante un petit air. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Les légumes sont dans le panier. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. On souffle. Sami sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8051,6 +8127,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8218,6 +8295,7 @@
           <t>narrateur|Sami s'approche de la poule. Le sable est tiède. On compte jusqu'à trois. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Le travail de l'adulte aide. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Sami prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8385,6 +8463,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8552,6 +8631,7 @@
           <t>narrateur|Sami prend un yaourt. Une cloche tinte au loin. Le yaourt est froid. Papa rappelle le travail. Acheter pain, légumes, chaussures. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8741,6 +8821,11 @@
       <c r="AW45" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -8910,6 +8995,7 @@
           <t>narrateur|Sami s'approche de le chat. Un rire court, tout petit. On montre du doigt. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Le pain est là. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9077,6 +9163,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9244,6 +9331,11 @@
           <t>narrateur|Sami s'approche de le chien. Le papier froisse, chut. On range la chaise. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Les chaussures attendent près de la porte. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Papa serre Sami tout doux.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9411,6 +9503,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9578,6 +9671,7 @@
           <t>narrateur|Sami s'approche de la poule. L'herbe chatouille le mollet. On range un objet. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Les légumes sont dans le panier. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9745,6 +9839,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9912,6 +10007,7 @@
           <t>narrateur|Sami prend un morceau de pain. Un oiseau chante tout près. Le pain croustille. Acheter. Travail. Légumes. Chaussures. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10101,6 +10197,11 @@
       <c r="AW53" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -10271,6 +10372,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10438,6 +10540,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10605,6 +10708,11 @@
           <t>narrateur|Sami s'approche de le chien. La fenêtre vibre un peu. On dit merci. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Le pain est là. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. On souffle. Sami sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10772,6 +10880,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10939,6 +11048,7 @@
           <t>narrateur|Sami s'approche de la poule. Le lait est froid dans le verre. On souffle doucement. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Les chaussures attendent près de la porte. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Sami prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11106,6 +11216,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11275,6 +11386,7 @@
 narrateur|Le pain. Les chaussures. Le travail aide. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11458,6 +11570,7 @@
           <t>narrateur|On achète le pain, et aussi quoi ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11629,6 +11742,7 @@
           <t>narrateur|Sami retient. Travail. Acheter pain, légumes, chaussures. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11820,6 +11934,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11987,6 +12102,7 @@
           <t>narrateur|Sami prend une pomme. Le savon glisse. Sami sent la pomme. Travail. Acheter pain, légumes, chaussures. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12176,6 +12292,11 @@
       <c r="AW65" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -12345,6 +12466,7 @@
           <t>narrateur|Sami s'approche de le chat. La corde du sac est rêche. On écoute jusqu'au bout. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Les légumes sont dans le panier. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12512,6 +12634,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12679,6 +12802,11 @@
           <t>narrateur|Sami s'approche de le chien. Le savon mousse entre les doigts. On attend son tour. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Le travail de l'adulte aide. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Papa serre Sami tout doux.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12846,6 +12974,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13013,6 +13142,7 @@
           <t>narrateur|Sami s'approche de la poule. Un ruisseau chante. On sourit ensemble. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Le pain est là. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13180,6 +13310,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13347,6 +13478,7 @@
           <t>narrateur|Sami prend un yaourt. Un ruisseau chante. Sami pose le yaourt. Papa dit encore : acheter. Pain. Légumes. Chaussures. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13536,6 +13668,11 @@
       <c r="AW73" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -13706,6 +13843,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13873,6 +14011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14040,6 +14179,11 @@
           <t>narrateur|Sami s'approche de le chien. Un pain croustille. On parle tout bas. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Les légumes sont dans le panier. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. On souffle. Sami sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14207,6 +14351,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14374,6 +14519,7 @@
           <t>narrateur|Sami s'approche de la poule. Le savon glisse. On range les jouets. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Le travail de l'adulte aide. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Sami prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14541,6 +14687,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14708,6 +14855,7 @@
           <t>narrateur|Sami prend un morceau de pain. Un ballon frotte le sol. Le pain est sur la table. Travail. Acheter pain, légumes, chaussures. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14897,6 +15045,11 @@
       <c r="AW81" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -15066,6 +15219,7 @@
           <t>narrateur|Sami s'approche de le chat. Une plume vole. On s'assoit un moment. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Le pain est là. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Sami dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15233,6 +15387,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15400,6 +15555,11 @@
           <t>narrateur|Sami s'approche de le chien. Le banc est lisse. On respire, un, deux. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Les chaussures attendent près de la porte. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Papa serre Sami tout doux.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15567,6 +15727,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15734,6 +15895,7 @@
           <t>narrateur|Sami s'approche de la poule. Un grelot sonne. On referme le sac. Papa ou maman travaille. On peut acheter pain, légumes, chaussures. Les légumes sont dans le panier. Papa ou maman travaille. L'argent sert à acheter pain, légumes, chaussures. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15901,6 +16063,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15919,7 +16082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15943,6 +16106,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15957,7 +16134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16144,6 +16321,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
